--- a/Pruebas calificadas/COLEGIO-JOSE-EUSTASIO-RIVERA-(IED)-501_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-JOSE-EUSTASIO-RIVERA-(IED)-501_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18959,7 +18959,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -21481,7 +21481,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-JOSE-EUSTASIO-RIVERA-(IED)-501_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-JOSE-EUSTASIO-RIVERA-(IED)-501_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2056,11 +2036,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -2068,7 +2044,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2305,11 +2281,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -2317,7 +2289,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2558,11 +2530,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -2570,7 +2538,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2811,11 +2779,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -2823,7 +2787,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3064,11 +3028,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -3076,7 +3036,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3317,11 +3277,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -3329,7 +3285,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3570,11 +3526,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -3582,7 +3534,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3823,11 +3775,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -3835,7 +3783,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4076,11 +4024,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -4088,7 +4032,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4329,11 +4273,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -4341,7 +4281,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4582,11 +4522,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -4594,7 +4530,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4835,11 +4771,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -4847,7 +4779,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5088,11 +5020,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -5100,7 +5028,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5341,11 +5269,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -5353,7 +5277,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5594,11 +5518,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -5606,7 +5526,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5847,11 +5767,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -5859,7 +5775,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6100,11 +6016,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -6112,7 +6024,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6353,11 +6265,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -6365,7 +6273,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6606,11 +6514,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -6618,7 +6522,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6859,11 +6763,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -6871,7 +6771,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7112,11 +7012,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -7124,7 +7020,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7365,11 +7261,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -7377,7 +7269,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7618,11 +7510,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -7630,7 +7518,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7867,11 +7755,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -7879,7 +7763,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8120,11 +8004,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -8132,7 +8012,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8373,11 +8253,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -8385,7 +8261,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8622,11 +8498,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -8634,7 +8506,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8875,11 +8747,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -8887,7 +8755,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9128,11 +8996,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -9140,7 +9004,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9381,11 +9245,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -9393,7 +9253,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9634,11 +9494,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -9646,7 +9502,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9887,11 +9743,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -9899,7 +9751,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10140,11 +9992,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -10152,7 +10000,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10393,11 +10241,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -10405,7 +10249,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10646,11 +10490,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -10658,7 +10498,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10899,11 +10739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -10911,7 +10747,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11152,11 +10988,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -11164,7 +10996,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11405,11 +11237,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -11417,7 +11245,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11658,11 +11486,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -11670,7 +11494,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11907,11 +11731,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -11919,7 +11739,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12160,11 +11980,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -12172,7 +11988,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12413,11 +12229,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -12425,7 +12237,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12666,11 +12478,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -12678,7 +12486,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12919,11 +12727,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -12931,7 +12735,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13168,11 +12972,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -13180,7 +12980,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13421,11 +13221,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -13433,7 +13229,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13674,11 +13470,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -13686,7 +13478,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13927,11 +13719,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -13939,7 +13727,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14180,11 +13968,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -14192,7 +13976,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14433,11 +14217,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -14445,7 +14225,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14686,11 +14466,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -14698,7 +14474,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14939,11 +14715,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -14951,7 +14723,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15192,11 +14964,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -15204,7 +14972,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15445,11 +15213,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -15457,7 +15221,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15698,11 +15462,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -15710,7 +15470,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15951,11 +15711,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -15963,7 +15719,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16204,11 +15960,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -16216,7 +15968,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16457,11 +16209,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -16469,7 +16217,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16706,11 +16454,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -16718,7 +16462,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16959,11 +16703,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -16971,7 +16711,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17212,11 +16952,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -17224,7 +16960,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17457,11 +17193,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -17469,7 +17201,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17710,11 +17442,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -17722,7 +17450,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17963,11 +17691,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -17975,7 +17699,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18192,11 +17916,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -18204,7 +17924,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18445,11 +18165,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -18457,7 +18173,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18694,11 +18410,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -18706,7 +18418,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18947,11 +18659,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -18959,7 +18667,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19200,11 +18908,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -19212,7 +18916,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19453,11 +19157,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -19465,7 +19165,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19706,11 +19406,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -19718,7 +19414,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19959,11 +19655,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -19971,7 +19663,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20208,11 +19900,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -20220,7 +19908,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20457,11 +20145,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -20469,7 +20153,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20710,11 +20394,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -20722,7 +20402,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -20963,11 +20643,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -20975,7 +20651,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -21216,11 +20892,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -21228,7 +20900,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -21469,11 +21141,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -21481,7 +21149,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -21722,11 +21390,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -21734,7 +21398,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -21971,11 +21635,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -21983,7 +21643,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -22224,11 +21884,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -22236,7 +21892,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -22477,11 +22133,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -22489,7 +22141,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -22730,11 +22382,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
           <t>111001800562</t>
@@ -22742,7 +22390,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE EUSTASIO RIVERA (IED)</t>
+          <t>COLEGIO JOSE EUSTASIO RIVERA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
